--- a/nr-doc-core-condition/ig/ValueSet-fr-core-vs-bp-method.xlsx
+++ b/nr-doc-core-condition/ig/ValueSet-fr-core-vs-bp-method.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07T15:17:25+00:00</t>
+    <t>2026-09-14T12:24:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-doc-core-condition/ig/ValueSet-fr-core-vs-bp-method.xlsx
+++ b/nr-doc-core-condition/ig/ValueSet-fr-core-vs-bp-method.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T12:24:46+00:00</t>
+    <t>2026-09-14T12:47:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-doc-core-condition/ig/ValueSet-fr-core-vs-bp-method.xlsx
+++ b/nr-doc-core-condition/ig/ValueSet-fr-core-vs-bp-method.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T12:47:40+00:00</t>
+    <t>2026-09-16T08:14:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-doc-core-condition/ig/ValueSet-fr-core-vs-bp-method.xlsx
+++ b/nr-doc-core-condition/ig/ValueSet-fr-core-vs-bp-method.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-16T08:14:25+00:00</t>
+    <t>2026-09-16T15:45:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-doc-core-condition/ig/ValueSet-fr-core-vs-bp-method.xlsx
+++ b/nr-doc-core-condition/ig/ValueSet-fr-core-vs-bp-method.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-16T15:45:09+00:00</t>
+    <t>2026-09-17T13:23:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-doc-core-condition/ig/ValueSet-fr-core-vs-bp-method.xlsx
+++ b/nr-doc-core-condition/ig/ValueSet-fr-core-vs-bp-method.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-17T13:23:37+00:00</t>
+    <t>2026-10-13T12:11:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
